--- a/내투자대시보드/투자원장_샘플.xlsx
+++ b/내투자대시보드/투자원장_샘플.xlsx
@@ -5524,7 +5524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5593,7 +5593,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5610,10 +5610,10 @@
         <v>30</v>
       </c>
       <c r="E5" t="n">
-        <v>238.52</v>
+        <v>560</v>
       </c>
       <c r="F5" t="n">
-        <v>7155.6</v>
+        <v>16800</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -5624,27 +5624,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>VOO</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Invesco QQQ Trust</t>
+          <t>Vanguard S&amp;P 500 ETF</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="E6" t="n">
-        <v>593.48</v>
+        <v>551.3</v>
       </c>
       <c r="F6" t="n">
-        <v>8308.719999999999</v>
+        <v>16539</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -5655,91 +5655,3656 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>VOO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Apple Inc.</t>
+          <t>Vanguard S&amp;P 500 ETF</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="E7" t="n">
-        <v>375.01</v>
+        <v>609.49</v>
       </c>
       <c r="F7" t="n">
-        <v>22500.6</v>
+        <v>18284.7</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>해외주식</t>
+          <t>해외ETF</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>VOO</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Microsoft Corp.</t>
+          <t>Vanguard S&amp;P 500 ETF</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E8" t="n">
-        <v>303.42</v>
+        <v>604.9299999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>7585.5</v>
+        <v>18147.9</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>해외주식</t>
+          <t>해외ETF</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>VOO</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Vanguard S&amp;P 500 ETF</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>30</v>
+      </c>
+      <c r="E9" t="n">
+        <v>629.22</v>
+      </c>
+      <c r="F9" t="n">
+        <v>18876.6</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>해외ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>VOO</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Vanguard S&amp;P 500 ETF</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>30</v>
+      </c>
+      <c r="E10" t="n">
+        <v>644.47</v>
+      </c>
+      <c r="F10" t="n">
+        <v>19334.1</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>해외ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>VOO</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Vanguard S&amp;P 500 ETF</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>30</v>
+      </c>
+      <c r="E11" t="n">
+        <v>663.4</v>
+      </c>
+      <c r="F11" t="n">
+        <v>19902</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>해외ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>VOO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Vanguard S&amp;P 500 ETF</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>34</v>
+      </c>
+      <c r="E12" t="n">
+        <v>676.77</v>
+      </c>
+      <c r="F12" t="n">
+        <v>23010.18</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>해외ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>VOO</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Vanguard S&amp;P 500 ETF</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>34</v>
+      </c>
+      <c r="E13" t="n">
+        <v>726.92</v>
+      </c>
+      <c r="F13" t="n">
+        <v>24715.28</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>해외ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>VOO</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Vanguard S&amp;P 500 ETF</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>37</v>
+      </c>
+      <c r="E14" t="n">
+        <v>754.96</v>
+      </c>
+      <c r="F14" t="n">
+        <v>27933.52</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>해외ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>VOO</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Vanguard S&amp;P 500 ETF</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>37</v>
+      </c>
+      <c r="E15" t="n">
+        <v>782.76</v>
+      </c>
+      <c r="F15" t="n">
+        <v>28962.12</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>해외ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>VOO</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Vanguard S&amp;P 500 ETF</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>37</v>
+      </c>
+      <c r="E16" t="n">
+        <v>806.1900000000001</v>
+      </c>
+      <c r="F16" t="n">
+        <v>29829.03</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>해외ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>VOO</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Vanguard S&amp;P 500 ETF</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>37</v>
+      </c>
+      <c r="E17" t="n">
+        <v>861.99</v>
+      </c>
+      <c r="F17" t="n">
+        <v>31893.63</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>해외ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>VOO</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Vanguard S&amp;P 500 ETF</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>37</v>
+      </c>
+      <c r="E18" t="n">
+        <v>880.13</v>
+      </c>
+      <c r="F18" t="n">
+        <v>32564.81</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>해외ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>VOO</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Vanguard S&amp;P 500 ETF</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>37</v>
+      </c>
+      <c r="E19" t="n">
+        <v>928.09</v>
+      </c>
+      <c r="F19" t="n">
+        <v>34339.33</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>해외ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>VOO</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Vanguard S&amp;P 500 ETF</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>37</v>
+      </c>
+      <c r="E20" t="n">
+        <v>984.15</v>
+      </c>
+      <c r="F20" t="n">
+        <v>36413.55</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>해외ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>VOO</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Vanguard S&amp;P 500 ETF</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>37</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1039.28</v>
+      </c>
+      <c r="F21" t="n">
+        <v>38453.36</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>해외ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>VOO</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Vanguard S&amp;P 500 ETF</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>37</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1064.11</v>
+      </c>
+      <c r="F22" t="n">
+        <v>39372.07</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>해외ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>VOO</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Vanguard S&amp;P 500 ETF</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>37</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1047.58</v>
+      </c>
+      <c r="F23" t="n">
+        <v>38760.46</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>해외ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>VOO</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Vanguard S&amp;P 500 ETF</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>38</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1055.09</v>
+      </c>
+      <c r="F24" t="n">
+        <v>40093.42</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>해외ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>VOO</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Vanguard S&amp;P 500 ETF</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>42</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1037.5</v>
+      </c>
+      <c r="F25" t="n">
+        <v>43575</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>해외ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>VOO</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Vanguard S&amp;P 500 ETF</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>44</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1064.61</v>
+      </c>
+      <c r="F26" t="n">
+        <v>46842.84</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>해외ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>VOO</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Vanguard S&amp;P 500 ETF</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>44</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1085.67</v>
+      </c>
+      <c r="F27" t="n">
+        <v>47769.48</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>해외ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>VOO</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Vanguard S&amp;P 500 ETF</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>48</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1070.89</v>
+      </c>
+      <c r="F28" t="n">
+        <v>51402.72</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>해외ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Invesco QQQ Trust</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>14</v>
+      </c>
+      <c r="E29" t="n">
+        <v>470</v>
+      </c>
+      <c r="F29" t="n">
+        <v>6580</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>해외ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Invesco QQQ Trust</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>14</v>
+      </c>
+      <c r="E30" t="n">
+        <v>463.59</v>
+      </c>
+      <c r="F30" t="n">
+        <v>6490.26</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>해외ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Invesco QQQ Trust</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>14</v>
+      </c>
+      <c r="E31" t="n">
+        <v>475.45</v>
+      </c>
+      <c r="F31" t="n">
+        <v>6656.3</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>해외ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Invesco QQQ Trust</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>14</v>
+      </c>
+      <c r="E32" t="n">
+        <v>578.11</v>
+      </c>
+      <c r="F32" t="n">
+        <v>8093.54</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>해외ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Invesco QQQ Trust</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>14</v>
+      </c>
+      <c r="E33" t="n">
+        <v>536.34</v>
+      </c>
+      <c r="F33" t="n">
+        <v>7508.76</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>해외ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Invesco QQQ Trust</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>14</v>
+      </c>
+      <c r="E34" t="n">
+        <v>534.86</v>
+      </c>
+      <c r="F34" t="n">
+        <v>7488.04</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>해외ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Invesco QQQ Trust</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>14</v>
+      </c>
+      <c r="E35" t="n">
+        <v>504.48</v>
+      </c>
+      <c r="F35" t="n">
+        <v>7062.72</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>해외ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Invesco QQQ Trust</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>14</v>
+      </c>
+      <c r="E36" t="n">
+        <v>493.48</v>
+      </c>
+      <c r="F36" t="n">
+        <v>6908.72</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>해외ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Invesco QQQ Trust</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>14</v>
+      </c>
+      <c r="E37" t="n">
+        <v>531.29</v>
+      </c>
+      <c r="F37" t="n">
+        <v>7438.06</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>해외ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Invesco QQQ Trust</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>16</v>
+      </c>
+      <c r="E38" t="n">
+        <v>541.66</v>
+      </c>
+      <c r="F38" t="n">
+        <v>8666.559999999999</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>해외ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Invesco QQQ Trust</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>16</v>
+      </c>
+      <c r="E39" t="n">
+        <v>551.17</v>
+      </c>
+      <c r="F39" t="n">
+        <v>8818.719999999999</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>해외ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Invesco QQQ Trust</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>16</v>
+      </c>
+      <c r="E40" t="n">
+        <v>556.76</v>
+      </c>
+      <c r="F40" t="n">
+        <v>8908.16</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>해외ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Invesco QQQ Trust</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>16</v>
+      </c>
+      <c r="E41" t="n">
+        <v>534.6799999999999</v>
+      </c>
+      <c r="F41" t="n">
+        <v>8554.879999999999</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>해외ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Invesco QQQ Trust</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>16</v>
+      </c>
+      <c r="E42" t="n">
+        <v>547.85</v>
+      </c>
+      <c r="F42" t="n">
+        <v>8765.6</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>해외ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Invesco QQQ Trust</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>16</v>
+      </c>
+      <c r="E43" t="n">
+        <v>525.33</v>
+      </c>
+      <c r="F43" t="n">
+        <v>8405.280000000001</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>해외ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Invesco QQQ Trust</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>16</v>
+      </c>
+      <c r="E44" t="n">
+        <v>534.63</v>
+      </c>
+      <c r="F44" t="n">
+        <v>8554.08</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>해외ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Invesco QQQ Trust</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>16</v>
+      </c>
+      <c r="E45" t="n">
+        <v>552.5700000000001</v>
+      </c>
+      <c r="F45" t="n">
+        <v>8841.120000000001</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>해외ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Invesco QQQ Trust</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>16</v>
+      </c>
+      <c r="E46" t="n">
+        <v>579.6</v>
+      </c>
+      <c r="F46" t="n">
+        <v>9273.6</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>해외ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Invesco QQQ Trust</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>16</v>
+      </c>
+      <c r="E47" t="n">
+        <v>607.29</v>
+      </c>
+      <c r="F47" t="n">
+        <v>9716.639999999999</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>해외ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Invesco QQQ Trust</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>16</v>
+      </c>
+      <c r="E48" t="n">
+        <v>622.49</v>
+      </c>
+      <c r="F48" t="n">
+        <v>9959.84</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>해외ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Invesco QQQ Trust</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>16</v>
+      </c>
+      <c r="E49" t="n">
+        <v>572.73</v>
+      </c>
+      <c r="F49" t="n">
+        <v>9163.68</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>해외ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Invesco QQQ Trust</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>16</v>
+      </c>
+      <c r="E50" t="n">
+        <v>564.54</v>
+      </c>
+      <c r="F50" t="n">
+        <v>9032.639999999999</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>해외ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Invesco QQQ Trust</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>16</v>
+      </c>
+      <c r="E51" t="n">
+        <v>582.53</v>
+      </c>
+      <c r="F51" t="n">
+        <v>9320.48</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>해외ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Invesco QQQ Trust</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>16</v>
+      </c>
+      <c r="E52" t="n">
+        <v>562.85</v>
+      </c>
+      <c r="F52" t="n">
+        <v>9005.6</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>해외ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>60</v>
+      </c>
+      <c r="E53" t="n">
+        <v>210</v>
+      </c>
+      <c r="F53" t="n">
+        <v>12600</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>해외주식</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>60</v>
+      </c>
+      <c r="E54" t="n">
+        <v>215.51</v>
+      </c>
+      <c r="F54" t="n">
+        <v>12930.6</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>해외주식</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>61</v>
+      </c>
+      <c r="E55" t="n">
+        <v>210.19</v>
+      </c>
+      <c r="F55" t="n">
+        <v>12821.59</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>해외주식</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>61</v>
+      </c>
+      <c r="E56" t="n">
+        <v>196.74</v>
+      </c>
+      <c r="F56" t="n">
+        <v>12001.14</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>해외주식</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>61</v>
+      </c>
+      <c r="E57" t="n">
+        <v>195.37</v>
+      </c>
+      <c r="F57" t="n">
+        <v>11917.57</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>해외주식</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>61</v>
+      </c>
+      <c r="E58" t="n">
+        <v>205.64</v>
+      </c>
+      <c r="F58" t="n">
+        <v>12544.04</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>해외주식</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>61</v>
+      </c>
+      <c r="E59" t="n">
+        <v>207.85</v>
+      </c>
+      <c r="F59" t="n">
+        <v>12678.85</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>해외주식</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>61</v>
+      </c>
+      <c r="E60" t="n">
+        <v>201.07</v>
+      </c>
+      <c r="F60" t="n">
+        <v>12265.27</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>해외주식</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>61</v>
+      </c>
+      <c r="E61" t="n">
+        <v>197.16</v>
+      </c>
+      <c r="F61" t="n">
+        <v>12026.76</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>해외주식</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>61</v>
+      </c>
+      <c r="E62" t="n">
+        <v>194.13</v>
+      </c>
+      <c r="F62" t="n">
+        <v>11841.93</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>해외주식</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>61</v>
+      </c>
+      <c r="E63" t="n">
+        <v>195.8</v>
+      </c>
+      <c r="F63" t="n">
+        <v>11943.8</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>해외주식</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>61</v>
+      </c>
+      <c r="E64" t="n">
+        <v>197.82</v>
+      </c>
+      <c r="F64" t="n">
+        <v>12067.02</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>해외주식</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>65</v>
+      </c>
+      <c r="E65" t="n">
+        <v>191.27</v>
+      </c>
+      <c r="F65" t="n">
+        <v>12432.55</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>해외주식</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>65</v>
+      </c>
+      <c r="E66" t="n">
+        <v>175.47</v>
+      </c>
+      <c r="F66" t="n">
+        <v>11405.55</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>해외주식</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>65</v>
+      </c>
+      <c r="E67" t="n">
+        <v>180.14</v>
+      </c>
+      <c r="F67" t="n">
+        <v>11709.1</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>해외주식</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>65</v>
+      </c>
+      <c r="E68" t="n">
+        <v>181.07</v>
+      </c>
+      <c r="F68" t="n">
+        <v>11769.55</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>해외주식</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>65</v>
+      </c>
+      <c r="E69" t="n">
+        <v>192.69</v>
+      </c>
+      <c r="F69" t="n">
+        <v>12524.85</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>해외주식</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>65</v>
+      </c>
+      <c r="E70" t="n">
+        <v>192.3</v>
+      </c>
+      <c r="F70" t="n">
+        <v>12499.5</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>해외주식</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>65</v>
+      </c>
+      <c r="E71" t="n">
+        <v>180.86</v>
+      </c>
+      <c r="F71" t="n">
+        <v>11755.9</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>해외주식</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>65</v>
+      </c>
+      <c r="E72" t="n">
+        <v>161.13</v>
+      </c>
+      <c r="F72" t="n">
+        <v>10473.45</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>해외주식</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>65</v>
+      </c>
+      <c r="E73" t="n">
+        <v>140.07</v>
+      </c>
+      <c r="F73" t="n">
+        <v>9104.549999999999</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>해외주식</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>65</v>
+      </c>
+      <c r="E74" t="n">
+        <v>141.07</v>
+      </c>
+      <c r="F74" t="n">
+        <v>9169.549999999999</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>해외주식</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>65</v>
+      </c>
+      <c r="E75" t="n">
+        <v>143.62</v>
+      </c>
+      <c r="F75" t="n">
+        <v>9335.299999999999</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>해외주식</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>65</v>
+      </c>
+      <c r="E76" t="n">
+        <v>172.9</v>
+      </c>
+      <c r="F76" t="n">
+        <v>11238.5</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>해외주식</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Microsoft Corp.</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>25</v>
+      </c>
+      <c r="E77" t="n">
+        <v>430</v>
+      </c>
+      <c r="F77" t="n">
+        <v>10750</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>해외주식</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Microsoft Corp.</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>29</v>
+      </c>
+      <c r="E78" t="n">
+        <v>409.75</v>
+      </c>
+      <c r="F78" t="n">
+        <v>11882.75</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>해외주식</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Microsoft Corp.</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>31</v>
+      </c>
+      <c r="E79" t="n">
+        <v>388.36</v>
+      </c>
+      <c r="F79" t="n">
+        <v>12039.16</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>해외주식</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Microsoft Corp.</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>31</v>
+      </c>
+      <c r="E80" t="n">
+        <v>421.61</v>
+      </c>
+      <c r="F80" t="n">
+        <v>13069.91</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>해외주식</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Microsoft Corp.</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>32</v>
+      </c>
+      <c r="E81" t="n">
+        <v>396.7</v>
+      </c>
+      <c r="F81" t="n">
+        <v>12694.4</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>해외주식</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Microsoft Corp.</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>32</v>
+      </c>
+      <c r="E82" t="n">
+        <v>364.23</v>
+      </c>
+      <c r="F82" t="n">
+        <v>11655.36</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>해외주식</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Microsoft Corp.</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>32</v>
+      </c>
+      <c r="E83" t="n">
+        <v>366.52</v>
+      </c>
+      <c r="F83" t="n">
+        <v>11728.64</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>해외주식</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Microsoft Corp.</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>32</v>
+      </c>
+      <c r="E84" t="n">
+        <v>392.97</v>
+      </c>
+      <c r="F84" t="n">
+        <v>12575.04</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>해외주식</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Microsoft Corp.</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>32</v>
+      </c>
+      <c r="E85" t="n">
+        <v>418.54</v>
+      </c>
+      <c r="F85" t="n">
+        <v>13393.28</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>해외주식</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Microsoft Corp.</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>32</v>
+      </c>
+      <c r="E86" t="n">
+        <v>403.69</v>
+      </c>
+      <c r="F86" t="n">
+        <v>12918.08</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>해외주식</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Microsoft Corp.</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>32</v>
+      </c>
+      <c r="E87" t="n">
+        <v>392.13</v>
+      </c>
+      <c r="F87" t="n">
+        <v>12548.16</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>해외주식</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Microsoft Corp.</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>32</v>
+      </c>
+      <c r="E88" t="n">
+        <v>378.93</v>
+      </c>
+      <c r="F88" t="n">
+        <v>12125.76</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>해외주식</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Microsoft Corp.</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>32</v>
+      </c>
+      <c r="E89" t="n">
+        <v>400.12</v>
+      </c>
+      <c r="F89" t="n">
+        <v>12803.84</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>해외주식</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Microsoft Corp.</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>32</v>
+      </c>
+      <c r="E90" t="n">
+        <v>377.06</v>
+      </c>
+      <c r="F90" t="n">
+        <v>12065.92</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>해외주식</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Microsoft Corp.</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>32</v>
+      </c>
+      <c r="E91" t="n">
+        <v>380.51</v>
+      </c>
+      <c r="F91" t="n">
+        <v>12176.32</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>해외주식</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Microsoft Corp.</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>32</v>
+      </c>
+      <c r="E92" t="n">
+        <v>391.41</v>
+      </c>
+      <c r="F92" t="n">
+        <v>12525.12</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>해외주식</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Microsoft Corp.</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>32</v>
+      </c>
+      <c r="E93" t="n">
+        <v>385.82</v>
+      </c>
+      <c r="F93" t="n">
+        <v>12346.24</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>해외주식</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Microsoft Corp.</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>32</v>
+      </c>
+      <c r="E94" t="n">
+        <v>400.82</v>
+      </c>
+      <c r="F94" t="n">
+        <v>12826.24</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>해외주식</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Microsoft Corp.</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>32</v>
+      </c>
+      <c r="E95" t="n">
+        <v>393.23</v>
+      </c>
+      <c r="F95" t="n">
+        <v>12583.36</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>해외주식</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Microsoft Corp.</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>32</v>
+      </c>
+      <c r="E96" t="n">
+        <v>397.29</v>
+      </c>
+      <c r="F96" t="n">
+        <v>12713.28</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>해외주식</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Microsoft Corp.</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>32</v>
+      </c>
+      <c r="E97" t="n">
+        <v>344.16</v>
+      </c>
+      <c r="F97" t="n">
+        <v>11013.12</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>해외주식</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Microsoft Corp.</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>32</v>
+      </c>
+      <c r="E98" t="n">
+        <v>360.91</v>
+      </c>
+      <c r="F98" t="n">
+        <v>11549.12</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>해외주식</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Microsoft Corp.</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>33</v>
+      </c>
+      <c r="E99" t="n">
+        <v>381.23</v>
+      </c>
+      <c r="F99" t="n">
+        <v>12580.59</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>해외주식</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Microsoft Corp.</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>36</v>
+      </c>
+      <c r="E100" t="n">
+        <v>352.65</v>
+      </c>
+      <c r="F100" t="n">
+        <v>12695.4</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>해외주식</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
         <is>
           <t>TLT</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C101" t="inlineStr">
         <is>
           <t>iShares 20+ Yr Treasury</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D101" t="n">
         <v>130</v>
       </c>
-      <c r="E9" t="n">
-        <v>263.55</v>
-      </c>
-      <c r="F9" t="n">
-        <v>34261.5</v>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="E101" t="n">
+        <v>92</v>
+      </c>
+      <c r="F101" t="n">
+        <v>11960</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>미국장기채</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>TLT</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>iShares 20+ Yr Treasury</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>130</v>
+      </c>
+      <c r="E102" t="n">
+        <v>96.42</v>
+      </c>
+      <c r="F102" t="n">
+        <v>12534.6</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>미국장기채</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>TLT</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>iShares 20+ Yr Treasury</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>130</v>
+      </c>
+      <c r="E103" t="n">
+        <v>101.33</v>
+      </c>
+      <c r="F103" t="n">
+        <v>13172.9</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>미국장기채</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>TLT</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>iShares 20+ Yr Treasury</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>130</v>
+      </c>
+      <c r="E104" t="n">
+        <v>102.61</v>
+      </c>
+      <c r="F104" t="n">
+        <v>13339.3</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>미국장기채</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>TLT</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>iShares 20+ Yr Treasury</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>130</v>
+      </c>
+      <c r="E105" t="n">
+        <v>103.87</v>
+      </c>
+      <c r="F105" t="n">
+        <v>13503.1</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>미국장기채</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>TLT</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>iShares 20+ Yr Treasury</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>133</v>
+      </c>
+      <c r="E106" t="n">
+        <v>101.26</v>
+      </c>
+      <c r="F106" t="n">
+        <v>13467.58</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>미국장기채</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>TLT</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>iShares 20+ Yr Treasury</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>135</v>
+      </c>
+      <c r="E107" t="n">
+        <v>97.56999999999999</v>
+      </c>
+      <c r="F107" t="n">
+        <v>13171.95</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>미국장기채</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>TLT</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>iShares 20+ Yr Treasury</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>136</v>
+      </c>
+      <c r="E108" t="n">
+        <v>94.76000000000001</v>
+      </c>
+      <c r="F108" t="n">
+        <v>12887.36</v>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>미국장기채</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>TLT</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>iShares 20+ Yr Treasury</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>136</v>
+      </c>
+      <c r="E109" t="n">
+        <v>88.93000000000001</v>
+      </c>
+      <c r="F109" t="n">
+        <v>12094.48</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>미국장기채</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>TLT</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>iShares 20+ Yr Treasury</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>136</v>
+      </c>
+      <c r="E110" t="n">
+        <v>90.44</v>
+      </c>
+      <c r="F110" t="n">
+        <v>12299.84</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>미국장기채</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>TLT</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>iShares 20+ Yr Treasury</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>136</v>
+      </c>
+      <c r="E111" t="n">
+        <v>93.15000000000001</v>
+      </c>
+      <c r="F111" t="n">
+        <v>12668.4</v>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>미국장기채</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>TLT</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>iShares 20+ Yr Treasury</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>136</v>
+      </c>
+      <c r="E112" t="n">
+        <v>95.43000000000001</v>
+      </c>
+      <c r="F112" t="n">
+        <v>12978.48</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>미국장기채</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>TLT</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>iShares 20+ Yr Treasury</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>136</v>
+      </c>
+      <c r="E113" t="n">
+        <v>97.33</v>
+      </c>
+      <c r="F113" t="n">
+        <v>13236.88</v>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>미국장기채</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>TLT</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>iShares 20+ Yr Treasury</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>136</v>
+      </c>
+      <c r="E114" t="n">
+        <v>98.42</v>
+      </c>
+      <c r="F114" t="n">
+        <v>13385.12</v>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>미국장기채</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>TLT</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>iShares 20+ Yr Treasury</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>136</v>
+      </c>
+      <c r="E115" t="n">
+        <v>99.02</v>
+      </c>
+      <c r="F115" t="n">
+        <v>13466.72</v>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>미국장기채</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>TLT</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>iShares 20+ Yr Treasury</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>136</v>
+      </c>
+      <c r="E116" t="n">
+        <v>98.41</v>
+      </c>
+      <c r="F116" t="n">
+        <v>13383.76</v>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>미국장기채</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>TLT</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>iShares 20+ Yr Treasury</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>136</v>
+      </c>
+      <c r="E117" t="n">
+        <v>98</v>
+      </c>
+      <c r="F117" t="n">
+        <v>13328</v>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>미국장기채</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>TLT</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>iShares 20+ Yr Treasury</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>136</v>
+      </c>
+      <c r="E118" t="n">
+        <v>96.45999999999999</v>
+      </c>
+      <c r="F118" t="n">
+        <v>13118.56</v>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>미국장기채</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>TLT</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>iShares 20+ Yr Treasury</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>136</v>
+      </c>
+      <c r="E119" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="F119" t="n">
+        <v>13436.8</v>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>미국장기채</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>TLT</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>iShares 20+ Yr Treasury</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>136</v>
+      </c>
+      <c r="E120" t="n">
+        <v>101.78</v>
+      </c>
+      <c r="F120" t="n">
+        <v>13842.08</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>미국장기채</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>TLT</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>iShares 20+ Yr Treasury</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>136</v>
+      </c>
+      <c r="E121" t="n">
+        <v>106.08</v>
+      </c>
+      <c r="F121" t="n">
+        <v>14426.88</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>미국장기채</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>TLT</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>iShares 20+ Yr Treasury</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>136</v>
+      </c>
+      <c r="E122" t="n">
+        <v>101.11</v>
+      </c>
+      <c r="F122" t="n">
+        <v>13750.96</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>미국장기채</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>TLT</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>iShares 20+ Yr Treasury</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>136</v>
+      </c>
+      <c r="E123" t="n">
+        <v>102.46</v>
+      </c>
+      <c r="F123" t="n">
+        <v>13934.56</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>미국장기채</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>TLT</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>iShares 20+ Yr Treasury</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>136</v>
+      </c>
+      <c r="E124" t="n">
+        <v>99.69</v>
+      </c>
+      <c r="F124" t="n">
+        <v>13557.84</v>
+      </c>
+      <c r="G124" t="inlineStr">
         <is>
           <t>미국장기채</t>
         </is>

--- a/내투자대시보드/투자원장_샘플.xlsx
+++ b/내투자대시보드/투자원장_샘플.xlsx
@@ -13,6 +13,7 @@
     <sheet name="벤치마크" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="월말보유" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="목표" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="시장지표" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -9411,4 +9412,448 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>월말 시장지표 (자동수집 대상)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>미국채 10년 금리 · 금 · WTI 원유 월말 값.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>기준월
+(YYYY-MM)</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>미국채10년
+(%)</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>금
+(USD/oz)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>WTI
+(USD/bbl)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2269</v>
+      </c>
+      <c r="D5" t="n">
+        <v>77.84</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2199</v>
+      </c>
+      <c r="D6" t="n">
+        <v>73.51000000000001</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2344</v>
+      </c>
+      <c r="D7" t="n">
+        <v>83.7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2284</v>
+      </c>
+      <c r="D8" t="n">
+        <v>82.12</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2405</v>
+      </c>
+      <c r="D9" t="n">
+        <v>83.81</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2497</v>
+      </c>
+      <c r="D10" t="n">
+        <v>77.13</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2438</v>
+      </c>
+      <c r="D11" t="n">
+        <v>83.47</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2399</v>
+      </c>
+      <c r="D12" t="n">
+        <v>86.90000000000001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2337</v>
+      </c>
+      <c r="D13" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="C14" t="n">
+        <v>2395</v>
+      </c>
+      <c r="D14" t="n">
+        <v>87.26000000000001</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="C15" t="n">
+        <v>2496</v>
+      </c>
+      <c r="D15" t="n">
+        <v>98.33</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2676</v>
+      </c>
+      <c r="D16" t="n">
+        <v>97.83</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2703</v>
+      </c>
+      <c r="D17" t="n">
+        <v>97.89</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2777</v>
+      </c>
+      <c r="D18" t="n">
+        <v>103.82</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2779</v>
+      </c>
+      <c r="D19" t="n">
+        <v>89.89</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2782</v>
+      </c>
+      <c r="D20" t="n">
+        <v>92.66</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="C21" t="n">
+        <v>2824</v>
+      </c>
+      <c r="D21" t="n">
+        <v>97.20999999999999</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2896</v>
+      </c>
+      <c r="D22" t="n">
+        <v>100.23</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="C23" t="n">
+        <v>2850</v>
+      </c>
+      <c r="D23" t="n">
+        <v>92.42</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="C24" t="n">
+        <v>2723</v>
+      </c>
+      <c r="D24" t="n">
+        <v>93.41</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="C25" t="n">
+        <v>2615</v>
+      </c>
+      <c r="D25" t="n">
+        <v>91.58</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="C26" t="n">
+        <v>2650</v>
+      </c>
+      <c r="D26" t="n">
+        <v>92.90000000000001</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="C27" t="n">
+        <v>2616</v>
+      </c>
+      <c r="D27" t="n">
+        <v>98.70999999999999</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="C28" t="n">
+        <v>2701</v>
+      </c>
+      <c r="D28" t="n">
+        <v>95.20999999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/내투자대시보드/투자원장_샘플.xlsx
+++ b/내투자대시보드/투자원장_샘플.xlsx
@@ -13,7 +13,8 @@
     <sheet name="벤치마크" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="월말보유" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="목표" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="시장지표" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="배당" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="시장지표" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -9386,26 +9387,26 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10년 내 5억 만들기</t>
+          <t>1조 만들기</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>500000000</v>
+        <v>1000000000000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2036-07</t>
+          <t>2055-12</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>2000000</v>
       </c>
       <c r="E5" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>샘플 목표</t>
+          <t>기본 목표 (샘플)</t>
         </is>
       </c>
     </row>
@@ -9415,6 +9416,664 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>월별 배당 수령 (선택)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>종목별로 배당 받은 달에 한 줄. 자동수집도 채울 수 있음.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>기준월
+(YYYY-MM)</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>티커</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>배당금
+(USD)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>VOO</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>55.69</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>VOO</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>57.33</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>VOO</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>58.97</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>VOO</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>60.61</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>VOO</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>62.24</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>VOO</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>63.88</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>VOO</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>65.52</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>VOO</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>67.16</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>10.07</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>10.36</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>10.66</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>10.96</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>11.25</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>11.55</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>11.84</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>12.14</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>16.07</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>16.54</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>17.01</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>17.48</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>17.96</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>18.43</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>18.9</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>19.37</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>21.93</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>22.57</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>23.22</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>23.87</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>24.51</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>25.16</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>25.8</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>26.45</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>TLT</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>115.89</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>TLT</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>119.3</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>TLT</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>122.71</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>TLT</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>126.12</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>TLT</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>129.53</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>TLT</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>132.94</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>TLT</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>136.34</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>TLT</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>139.75</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/내투자대시보드/투자원장_샘플.xlsx
+++ b/내투자대시보드/투자원장_샘플.xlsx
@@ -15,6 +15,7 @@
     <sheet name="목표" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="배당" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="시장지표" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="심리" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20877,4 +20878,1315 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C88"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CNN Fear &amp; Greed (자동수집)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>기준일·score(0~100)·rating. 대시보드는 가장 최근 값을 사용.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>기준일
+(YYYY-MM-DD)</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>rating</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2019-01-28</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>46</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2019-02-28</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>34</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Fear</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2019-03-28</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>31</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Fear</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2019-04-28</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>53</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2019-05-28</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>46</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2019-06-28</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>40</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Fear</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2019-07-28</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>27</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Fear</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2019-08-28</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>35</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Fear</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2019-09-28</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>57</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Greed</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2019-10-28</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>64</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Greed</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2019-11-28</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>56</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Greed</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2019-12-28</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>64</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Greed</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2020-01-28</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>64</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Greed</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2020-02-28</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>52</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2020-03-28</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>45</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2020-04-28</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>39</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Fear</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2020-05-28</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>45</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2020-06-28</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>34</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Fear</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2020-07-28</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>43</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Fear</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2020-08-28</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>50</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2020-09-28</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>56</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Greed</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2020-10-28</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>69</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Greed</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2020-11-28</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>60</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Greed</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2020-12-28</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>44</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Fear</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2021-01-28</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>41</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Fear</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2021-02-28</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>42</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Fear</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2021-03-28</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>33</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Fear</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2021-04-28</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>39</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Fear</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2021-05-28</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>22</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Extreme Fear</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2021-06-28</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>33</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Fear</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2021-07-28</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>31</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Fear</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2021-08-28</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>36</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Fear</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2021-09-28</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>33</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Fear</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2021-10-28</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>52</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>41</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Fear</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2021-12-28</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>40</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Fear</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2022-01-28</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>45</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2022-02-28</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>44</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Fear</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2022-03-28</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>68</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Greed</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2022-04-28</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>85</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Extreme Greed</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2022-05-28</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>86</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Extreme Greed</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2022-06-28</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>90</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Extreme Greed</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2022-07-28</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>90</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Extreme Greed</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2022-08-28</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>90</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Extreme Greed</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2022-09-28</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>67</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Greed</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2022-10-28</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>63</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Greed</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2022-11-28</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>62</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Greed</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2022-12-28</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>46</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2023-01-28</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>43</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Fear</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2023-02-28</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>41</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Fear</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2023-03-28</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>33</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Fear</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2023-04-28</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>23</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Extreme Fear</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2023-05-28</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>10</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Extreme Fear</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2023-06-28</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>21</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Extreme Fear</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2023-07-28</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>10</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Extreme Fear</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>18</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Extreme Fear</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>24</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Extreme Fear</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2023-10-28</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>19</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Extreme Fear</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2023-11-28</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>32</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Fear</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2023-12-28</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>23</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Extreme Fear</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2024-01-28</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>10</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Extreme Fear</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2024-02-28</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>11</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Extreme Fear</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2024-03-28</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>10</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Extreme Fear</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2024-04-28</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>10</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Extreme Fear</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>17</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Extreme Fear</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>22</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Extreme Fear</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>10</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Extreme Fear</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>10</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Extreme Fear</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>10</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Extreme Fear</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>15</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Extreme Fear</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>29</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Fear</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2024-12-28</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>32</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Fear</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2025-01-28</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>37</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Fear</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>24</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Extreme Fear</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>21</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Extreme Fear</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2025-04-28</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>30</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Fear</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>35</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Fear</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>44</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Fear</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>37</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Fear</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>59</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Greed</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>60</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Greed</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>62</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Greed</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>66</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Greed</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>58</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Greed</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/내투자대시보드/투자원장_샘플.xlsx
+++ b/내투자대시보드/투자원장_샘플.xlsx
@@ -11,8 +11,9 @@
     <sheet name="연별스냅샷" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="연말시장" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="연말보유" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="배당" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="목표" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="거래일지" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="배당" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="목표" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -440,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A23"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="64" customWidth="1" min="1" max="1"/>
@@ -490,95 +491,105 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>[자동수집이 채움]</t>
+          <t xml:space="preserve">  거래일지   — 사고판 기록 (있으면 '매매일지' 탭이 켜집니다 · 없어도 무방)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  연말시장   — 연말 USD/KRW·S&amp;P500·NASDAQ·다우</t>
-        </is>
-      </c>
+      <c r="A10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  연말보유   — 티커·수량·종가·평가액</t>
+          <t>[자동수집이 채움]</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  배당       — 연도·티커·배당금</t>
+          <t xml:space="preserve">  연말시장   — 연말 USD/KRW·S&amp;P500·NASDAQ·다우</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  연말보유   — 티커·수량·종가·평가액</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t xml:space="preserve">  배당       — 연도·티커·배당금</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>[원장에 없음 — 대시보드 HTML에 매일 자동으로 심깁니다]</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  시장지표(미국채10년·금·WTI) · Fear&amp;Greed · 미국 기준금리</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>자산군은 아래 6종만 사용합니다:</t>
+          <t xml:space="preserve">  시장지표(미국채10년·금·WTI) · Fear&amp;Greed · 미국 기준금리</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  · 해외주식</t>
-        </is>
-      </c>
+      <c r="A18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · 해외ETF</t>
+          <t>자산군은 아래 6종만 사용합니다:</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · 미국장기채</t>
+          <t xml:space="preserve">  · 해외주식</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · MMF</t>
+          <t xml:space="preserve">  · 해외ETF</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · RP</t>
+          <t xml:space="preserve">  · 미국장기채</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  · MMF</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  · RP</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t xml:space="preserve">  · 달러현금</t>
         </is>
@@ -2197,10 +2208,10 @@
         <v>20</v>
       </c>
       <c r="E5" t="n">
-        <v>250</v>
+        <v>282.88</v>
       </c>
       <c r="F5" t="n">
-        <v>5000</v>
+        <v>5657.6</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -2228,10 +2239,10 @@
         <v>20</v>
       </c>
       <c r="E6" t="n">
-        <v>288.87</v>
+        <v>347.44</v>
       </c>
       <c r="F6" t="n">
-        <v>5777.4</v>
+        <v>6948.8</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -2256,13 +2267,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E7" t="n">
-        <v>370.83</v>
+        <v>360.68</v>
       </c>
       <c r="F7" t="n">
-        <v>9641.58</v>
+        <v>7934.96</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -2287,13 +2298,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="E8" t="n">
-        <v>458.41</v>
+        <v>307.27</v>
       </c>
       <c r="F8" t="n">
-        <v>14210.71</v>
+        <v>6759.94</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -2318,13 +2329,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="E9" t="n">
-        <v>456.56</v>
+        <v>342.25</v>
       </c>
       <c r="F9" t="n">
-        <v>16892.72</v>
+        <v>9583</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -2349,13 +2360,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E10" t="n">
-        <v>502.5</v>
+        <v>365.37</v>
       </c>
       <c r="F10" t="n">
-        <v>20602.5</v>
+        <v>10595.73</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -2380,13 +2391,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="E11" t="n">
-        <v>522.9400000000001</v>
+        <v>312.45</v>
       </c>
       <c r="F11" t="n">
-        <v>24055.24</v>
+        <v>9373.5</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -2414,10 +2425,10 @@
         <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>170</v>
+        <v>196.31</v>
       </c>
       <c r="F12" t="n">
-        <v>1700</v>
+        <v>1963.1</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -2442,13 +2453,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>190</v>
+        <v>190.03</v>
       </c>
       <c r="F13" t="n">
-        <v>3040</v>
+        <v>2280.36</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -2473,13 +2484,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E14" t="n">
-        <v>182.85</v>
+        <v>201.99</v>
       </c>
       <c r="F14" t="n">
-        <v>4022.7</v>
+        <v>3433.83</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -2504,13 +2515,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E15" t="n">
-        <v>270.71</v>
+        <v>252.17</v>
       </c>
       <c r="F15" t="n">
-        <v>7038.46</v>
+        <v>5043.4</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -2535,13 +2546,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E16" t="n">
-        <v>298.87</v>
+        <v>215.23</v>
       </c>
       <c r="F16" t="n">
-        <v>8966.1</v>
+        <v>4304.6</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -2566,13 +2577,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="E17" t="n">
-        <v>404.05</v>
+        <v>279.61</v>
       </c>
       <c r="F17" t="n">
-        <v>12525.55</v>
+        <v>6431.03</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -2597,13 +2608,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="E18" t="n">
-        <v>428.7</v>
+        <v>408.42</v>
       </c>
       <c r="F18" t="n">
-        <v>15861.9</v>
+        <v>9393.66</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -2631,10 +2642,10 @@
         <v>40</v>
       </c>
       <c r="E19" t="n">
-        <v>55</v>
+        <v>63.15</v>
       </c>
       <c r="F19" t="n">
-        <v>2200</v>
+        <v>2526</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -2659,13 +2670,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E20" t="n">
-        <v>46.83</v>
+        <v>80.12</v>
       </c>
       <c r="F20" t="n">
-        <v>1873.2</v>
+        <v>3284.92</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -2690,13 +2701,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E21" t="n">
-        <v>37.11</v>
+        <v>106.43</v>
       </c>
       <c r="F21" t="n">
-        <v>1632.84</v>
+        <v>4576.49</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -2721,13 +2732,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E22" t="n">
-        <v>28.88</v>
+        <v>106.06</v>
       </c>
       <c r="F22" t="n">
-        <v>1415.12</v>
+        <v>4666.64</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -2755,10 +2766,10 @@
         <v>49</v>
       </c>
       <c r="E23" t="n">
-        <v>31.67</v>
+        <v>135.91</v>
       </c>
       <c r="F23" t="n">
-        <v>1551.83</v>
+        <v>6659.59</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -2783,13 +2794,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E24" t="n">
-        <v>40.03</v>
+        <v>167.88</v>
       </c>
       <c r="F24" t="n">
-        <v>2081.56</v>
+        <v>8394</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -2814,13 +2825,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E25" t="n">
-        <v>61.71</v>
+        <v>118.02</v>
       </c>
       <c r="F25" t="n">
-        <v>3517.47</v>
+        <v>6137.04</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -2848,10 +2859,10 @@
         <v>18</v>
       </c>
       <c r="E26" t="n">
-        <v>110</v>
+        <v>169.37</v>
       </c>
       <c r="F26" t="n">
-        <v>1980</v>
+        <v>3048.66</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -2876,13 +2887,13 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E27" t="n">
-        <v>105.24</v>
+        <v>289.21</v>
       </c>
       <c r="F27" t="n">
-        <v>2104.8</v>
+        <v>6941.04</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -2907,13 +2918,13 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E28" t="n">
-        <v>144.7</v>
+        <v>256.82</v>
       </c>
       <c r="F28" t="n">
-        <v>3472.8</v>
+        <v>7447.78</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -2938,13 +2949,13 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="E29" t="n">
-        <v>165.62</v>
+        <v>129.4</v>
       </c>
       <c r="F29" t="n">
-        <v>3974.88</v>
+        <v>4011.4</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -2969,13 +2980,13 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E30" t="n">
-        <v>189.28</v>
+        <v>115.04</v>
       </c>
       <c r="F30" t="n">
-        <v>5299.84</v>
+        <v>4141.44</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -3000,13 +3011,13 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E31" t="n">
-        <v>232.23</v>
+        <v>137.81</v>
       </c>
       <c r="F31" t="n">
-        <v>7895.82</v>
+        <v>5236.78</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -3031,13 +3042,13 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E32" t="n">
-        <v>192.92</v>
+        <v>132.64</v>
       </c>
       <c r="F32" t="n">
-        <v>7716.8</v>
+        <v>5703.52</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -3065,10 +3076,10 @@
         <v>90</v>
       </c>
       <c r="E33" t="n">
-        <v>130</v>
+        <v>129.69</v>
       </c>
       <c r="F33" t="n">
-        <v>11700</v>
+        <v>11672.1</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -3093,13 +3104,13 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E34" t="n">
-        <v>163.15</v>
+        <v>129.48</v>
       </c>
       <c r="F34" t="n">
-        <v>15662.4</v>
+        <v>11782.68</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -3124,13 +3135,13 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E35" t="n">
-        <v>165.08</v>
+        <v>111.32</v>
       </c>
       <c r="F35" t="n">
-        <v>16012.76</v>
+        <v>10686.72</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -3158,10 +3169,10 @@
         <v>97</v>
       </c>
       <c r="E36" t="n">
-        <v>167.06</v>
+        <v>93.39</v>
       </c>
       <c r="F36" t="n">
-        <v>16204.82</v>
+        <v>9058.83</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -3186,13 +3197,13 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E37" t="n">
-        <v>167.43</v>
+        <v>81.27</v>
       </c>
       <c r="F37" t="n">
-        <v>16743</v>
+        <v>8370.809999999999</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -3217,13 +3228,13 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E38" t="n">
-        <v>148.18</v>
+        <v>72.7</v>
       </c>
       <c r="F38" t="n">
-        <v>15558.9</v>
+        <v>7560.8</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -3248,13 +3259,13 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E39" t="n">
-        <v>119.13</v>
+        <v>64.83</v>
       </c>
       <c r="F39" t="n">
-        <v>12508.65</v>
+        <v>7131.3</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -3268,6 +3279,1229 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>거래일지 — 사고판 기록 (직접 입력 · 선택)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>이 기록이 있으면 '그때 안 했다면?' 을 계산해 매매 판정을 보여줍니다. 단가는 수수료·세금 포함가로 적으면 더 정확합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>거래일
+(YYYY-MM)</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>구분
+(매수/매도)</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>티커</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>수량</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>단가
+(USD)</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>통화</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>메모</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2019-05</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>매도</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Microsoft Corp.</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F5" t="n">
+        <v>120.14</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>겁나서 정리</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2019-06</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>매도</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>TLT</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>iShares 20+ Yr Treasury</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>124.38</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>고점 같아서 정리</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2019-07</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>매수</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>VOO</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Vanguard S&amp;P 500 ETF</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>276.82</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>떨어진 김에 추가</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2019-08</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>매도</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>TLT</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>iShares 20+ Yr Treasury</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" t="n">
+        <v>135.02</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>고점 같아서 정리</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2019-08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>매도</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>VOO</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Vanguard S&amp;P 500 ETF</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="n">
+        <v>263.62</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>겁나서 정리</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2019-11</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>매도</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Microsoft Corp.</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>15</v>
+      </c>
+      <c r="F10" t="n">
+        <v>169.37</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>고점 같아서 정리</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2020-02</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>매수</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Microsoft Corp.</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>12</v>
+      </c>
+      <c r="F11" t="n">
+        <v>174.61</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>쫓아 들어감</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2020-06</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>매수</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Invesco QQQ Trust</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>20</v>
+      </c>
+      <c r="F12" t="n">
+        <v>185.08</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>떨어진 김에 추가</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2020-08</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>매수</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Invesco QQQ Trust</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>15</v>
+      </c>
+      <c r="F13" t="n">
+        <v>180.02</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>떨어진 김에 추가</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2020-10</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>매수</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>VOO</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Vanguard S&amp;P 500 ETF</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>12</v>
+      </c>
+      <c r="F14" t="n">
+        <v>337.15</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>쫓아 들어감</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2021-01</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>매수</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>VOO</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Vanguard S&amp;P 500 ETF</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>20</v>
+      </c>
+      <c r="F15" t="n">
+        <v>328.65</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>쫓아 들어감</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2021-04</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>매도</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Invesco QQQ Trust</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>169.49</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>겁나서 정리</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2021-06</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>매도</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>20</v>
+      </c>
+      <c r="F17" t="n">
+        <v>91.42</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>겁나서 정리</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2021-06</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>매도</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Microsoft Corp.</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="n">
+        <v>238.64</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>고점 같아서 정리</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2021-08</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>매수</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>VOO</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Vanguard S&amp;P 500 ETF</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>320.08</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>쫓아 들어감</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2021-10</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>매수</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>VOO</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Vanguard S&amp;P 500 ETF</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>20</v>
+      </c>
+      <c r="F20" t="n">
+        <v>326.93</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>쫓아 들어감</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2021-11</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>매수</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>TLT</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>iShares 20+ Yr Treasury</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>15</v>
+      </c>
+      <c r="F21" t="n">
+        <v>118.82</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>쫓아 들어감</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2022-04</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>매도</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>8</v>
+      </c>
+      <c r="F22" t="n">
+        <v>98.93000000000001</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>겁나서 정리</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2022-10</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>매수</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Invesco QQQ Trust</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5</v>
+      </c>
+      <c r="F23" t="n">
+        <v>241.46</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>떨어진 김에 추가</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2023-01</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>매도</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>TLT</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>iShares 20+ Yr Treasury</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>20</v>
+      </c>
+      <c r="F24" t="n">
+        <v>94.11</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>고점 같아서 정리</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2023-03</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>매도</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>TLT</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>iShares 20+ Yr Treasury</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>20</v>
+      </c>
+      <c r="F25" t="n">
+        <v>94.23999999999999</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>고점 같아서 정리</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2023-04</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>매수</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Microsoft Corp.</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>10</v>
+      </c>
+      <c r="F26" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>떨어진 김에 추가</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2023-10</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>매수</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5</v>
+      </c>
+      <c r="F27" t="n">
+        <v>112.87</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>떨어진 김에 추가</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>매도</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>8</v>
+      </c>
+      <c r="F28" t="n">
+        <v>147.77</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>고점 같아서 정리</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>매수</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>TLT</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>iShares 20+ Yr Treasury</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>8</v>
+      </c>
+      <c r="F29" t="n">
+        <v>78.04000000000001</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>쫓아 들어감</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>매도</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Invesco QQQ Trust</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>8</v>
+      </c>
+      <c r="F30" t="n">
+        <v>229.3</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>겁나서 정리</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>매도</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Microsoft Corp.</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5</v>
+      </c>
+      <c r="F31" t="n">
+        <v>155.89</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>고점 같아서 정리</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>매수</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>8</v>
+      </c>
+      <c r="F32" t="n">
+        <v>164.77</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>쫓아 들어감</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>매수</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Invesco QQQ Trust</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>20</v>
+      </c>
+      <c r="F33" t="n">
+        <v>299.32</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>떨어진 김에 추가</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>매수</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>3</v>
+      </c>
+      <c r="F34" t="n">
+        <v>129.13</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>쫓아 들어감</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3332,7 +4566,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>12.63</v>
       </c>
     </row>
     <row r="6">
@@ -3347,7 +4581,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>15.84</v>
+        <v>24.39</v>
       </c>
     </row>
     <row r="7">
@@ -3362,7 +4596,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10.2</v>
+        <v>11.78</v>
       </c>
     </row>
     <row r="8">
@@ -3377,7 +4611,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>444.6</v>
+        <v>443.54</v>
       </c>
     </row>
     <row r="9">
@@ -3392,7 +4626,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>65</v>
+        <v>73.55</v>
       </c>
     </row>
     <row r="10">
@@ -3407,7 +4641,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>9.369999999999999</v>
+        <v>16.42</v>
       </c>
     </row>
     <row r="11">
@@ -3422,7 +4656,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>16.84</v>
+        <v>55.53</v>
       </c>
     </row>
     <row r="12">
@@ -3437,7 +4671,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>18.24</v>
+        <v>13.68</v>
       </c>
     </row>
     <row r="13">
@@ -3452,7 +4686,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>595.17</v>
+        <v>447.74</v>
       </c>
     </row>
     <row r="14">
@@ -3467,7 +4701,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>75.11</v>
+        <v>90.33</v>
       </c>
     </row>
     <row r="15">
@@ -3482,7 +4716,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8.16</v>
+        <v>22.88</v>
       </c>
     </row>
     <row r="16">
@@ -3497,7 +4731,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>27.78</v>
+        <v>59.58</v>
       </c>
     </row>
     <row r="17">
@@ -3512,7 +4746,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>24.14</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="18">
@@ -3527,7 +4761,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>608.48</v>
+        <v>406.1</v>
       </c>
     </row>
     <row r="19">
@@ -3542,7 +4776,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>125.34</v>
+        <v>103.15</v>
       </c>
     </row>
     <row r="20">
@@ -3557,7 +4791,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>7.08</v>
+        <v>23.33</v>
       </c>
     </row>
     <row r="21">
@@ -3572,7 +4806,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>31.8</v>
+        <v>32.09</v>
       </c>
     </row>
     <row r="22">
@@ -3587,7 +4821,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>42.23</v>
+        <v>30.26</v>
       </c>
     </row>
     <row r="23">
@@ -3602,7 +4836,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>615.78</v>
+        <v>344.24</v>
       </c>
     </row>
     <row r="24">
@@ -3617,7 +4851,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>184.74</v>
+        <v>87.88</v>
       </c>
     </row>
     <row r="25">
@@ -3632,7 +4866,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>7.76</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="26">
@@ -3647,7 +4881,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>42.4</v>
+        <v>33.13</v>
       </c>
     </row>
     <row r="27">
@@ -3662,7 +4896,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>53.8</v>
+        <v>25.83</v>
       </c>
     </row>
     <row r="28">
@@ -3677,7 +4911,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>636.23</v>
+        <v>318.09</v>
       </c>
     </row>
     <row r="29">
@@ -3692,7 +4926,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>219.61</v>
+        <v>124.58</v>
       </c>
     </row>
     <row r="30">
@@ -3707,7 +4941,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>10.41</v>
+        <v>41.97</v>
       </c>
     </row>
     <row r="31">
@@ -3722,7 +4956,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>63.17</v>
+        <v>41.89</v>
       </c>
     </row>
     <row r="32">
@@ -3737,7 +4971,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>75.15000000000001</v>
+        <v>38.59</v>
       </c>
     </row>
     <row r="33">
@@ -3752,7 +4986,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>591.24</v>
+        <v>287.31</v>
       </c>
     </row>
     <row r="34">
@@ -3767,7 +5001,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>267.83</v>
+        <v>137.74</v>
       </c>
     </row>
     <row r="35">
@@ -3782,7 +5016,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>17.59</v>
+        <v>30.69</v>
       </c>
     </row>
     <row r="36">
@@ -3797,7 +5031,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>61.73</v>
+        <v>45.63</v>
       </c>
     </row>
     <row r="37">
@@ -3812,7 +5046,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>95.17</v>
+        <v>56.36</v>
       </c>
     </row>
     <row r="38">
@@ -3827,7 +5061,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>475.33</v>
+        <v>270.99</v>
       </c>
     </row>
     <row r="39">
@@ -3842,7 +5076,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>312.72</v>
+        <v>121.86</v>
       </c>
     </row>
   </sheetData>
@@ -3850,7 +5084,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
